--- a/data/gravel/Enigma Endeavour Mk2 2025.xlsx
+++ b/data/gravel/Enigma Endeavour Mk2 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C72A2058-608A-BA44-89D7-B5C22637B9C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2581FB8E-5D4E-0448-AC39-8FE42B47CD45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25760" yWindow="-18960" windowWidth="25860" windowHeight="16640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4060" yWindow="820" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="103">
   <si>
     <t>brand</t>
   </si>
@@ -339,6 +339,9 @@
   </si>
   <si>
     <t>CSIX gravel</t>
+  </si>
+  <si>
+    <t>https://www.enigmabikes.com/cdn/shop/files/Endeavour-2025-Hero_2500x.jpg?v=1741961160</t>
   </si>
 </sst>
 </file>
@@ -749,6 +752,11 @@
         <v>100</v>
       </c>
     </row>
+    <row r="6" spans="1:21">
+      <c r="B6" t="s">
+        <v>102</v>
+      </c>
+    </row>
     <row r="7" spans="1:21">
       <c r="A7" t="s">
         <v>7</v>

--- a/data/gravel/Enigma Endeavour Mk2 2025.xlsx
+++ b/data/gravel/Enigma Endeavour Mk2 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2581FB8E-5D4E-0448-AC39-8FE42B47CD45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC647414-1BDA-7846-AE1E-DD1554FA78EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4060" yWindow="820" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="105">
   <si>
     <t>brand</t>
   </si>
@@ -302,9 +302,6 @@
     <t>a8:f34</t>
   </si>
   <si>
-    <t>pounds</t>
-  </si>
-  <si>
     <t>gravel</t>
   </si>
   <si>
@@ -342,6 +339,15 @@
   </si>
   <si>
     <t>https://www.enigmabikes.com/cdn/shop/files/Endeavour-2025-Hero_2500x.jpg?v=1741961160</t>
+  </si>
+  <si>
+    <t>GBP</t>
+  </si>
+  <si>
+    <t>location</t>
+  </si>
+  <si>
+    <t>Hailsham, East Sussex, United Kingdom</t>
   </si>
 </sst>
 </file>
@@ -706,7 +712,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U74"/>
+  <dimension ref="A1:U75"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -725,7 +731,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="3" spans="1:21">
@@ -749,12 +755,12 @@
         <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="6" spans="1:21">
       <c r="B6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="7" spans="1:21">
@@ -770,7 +776,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C8" s="5">
         <v>52</v>
@@ -785,10 +791,10 @@
         <v>58</v>
       </c>
       <c r="H8" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="I8" s="2" t="s">
         <v>93</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>94</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>11</v>
@@ -803,13 +809,13 @@
         <v>17</v>
       </c>
       <c r="N8" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="O8" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="O8" s="2" t="s">
+      <c r="P8" s="2" t="s">
         <v>96</v>
-      </c>
-      <c r="P8" s="2" t="s">
-        <v>97</v>
       </c>
       <c r="Q8" s="2" t="s">
         <v>22</v>
@@ -832,7 +838,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C9" s="5">
         <v>520</v>
@@ -1100,7 +1106,7 @@
         <v>18</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C14" s="5">
         <v>75</v>
@@ -1120,7 +1126,7 @@
         <v>19</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C15" s="5">
         <v>70.5</v>
@@ -1140,7 +1146,7 @@
         <v>20</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C16" s="5">
         <v>50</v>
@@ -1290,7 +1296,7 @@
         <v>395</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -1441,7 +1447,7 @@
         <v>84</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="38" spans="1:6">
@@ -1449,7 +1455,7 @@
         <v>85</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="39" spans="1:6">
@@ -1462,7 +1468,7 @@
         <v>46</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="41" spans="1:6">
@@ -1595,7 +1601,7 @@
         <v>67</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -1692,7 +1698,15 @@
         <v>81</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>89</v>
+        <v>102</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2">
+      <c r="A75" t="s">
+        <v>103</v>
+      </c>
+      <c r="B75" t="s">
+        <v>104</v>
       </c>
     </row>
   </sheetData>

--- a/data/gravel/Enigma Endeavour Mk2 2025.xlsx
+++ b/data/gravel/Enigma Endeavour Mk2 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC647414-1BDA-7846-AE1E-DD1554FA78EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C7F3E12-29AE-DE46-94AB-502D50CE4571}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="111">
   <si>
     <t>brand</t>
   </si>
@@ -348,6 +348,24 @@
   </si>
   <si>
     <t>Hailsham, East Sussex, United Kingdom</t>
+  </si>
+  <si>
+    <t>head_tube_d</t>
+  </si>
+  <si>
+    <t>headset_upper</t>
+  </si>
+  <si>
+    <t>headset_lower</t>
+  </si>
+  <si>
+    <t>fork_steerer</t>
+  </si>
+  <si>
+    <t>fork_steerer_d</t>
+  </si>
+  <si>
+    <t>fork_material</t>
   </si>
 </sst>
 </file>
@@ -712,7 +730,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U75"/>
+  <dimension ref="A1:U81"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -1535,177 +1553,207 @@
     </row>
     <row r="51" spans="1:2">
       <c r="A51" t="s">
-        <v>58</v>
-      </c>
-      <c r="B51" s="1" t="s">
-        <v>82</v>
+        <v>105</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" t="s">
-        <v>59</v>
+        <v>106</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" t="s">
-        <v>60</v>
-      </c>
-      <c r="B53">
-        <v>31.6</v>
+        <v>107</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" t="s">
-        <v>61</v>
-      </c>
-      <c r="B54" s="1" t="s">
-        <v>83</v>
+        <v>108</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" t="s">
-        <v>62</v>
-      </c>
-      <c r="B55">
-        <v>42</v>
+        <v>109</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" t="s">
-        <v>63</v>
+        <v>110</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" t="s">
-        <v>64</v>
-      </c>
-      <c r="B57">
-        <v>160</v>
+        <v>58</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" t="s">
-        <v>65</v>
-      </c>
-      <c r="B58">
-        <v>140</v>
+        <v>59</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" t="s">
-        <v>66</v>
+        <v>60</v>
+      </c>
+      <c r="B59">
+        <v>31.6</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>97</v>
+        <v>83</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" t="s">
-        <v>68</v>
+        <v>62</v>
+      </c>
+      <c r="B61">
+        <v>42</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" t="s">
-        <v>70</v>
+        <v>64</v>
+      </c>
+      <c r="B63">
+        <v>160</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="B64">
-        <v>2</v>
+        <v>140</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" t="s">
-        <v>72</v>
-      </c>
-      <c r="B65">
-        <v>1</v>
+        <v>66</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>48</v>
+        <v>97</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" t="s">
-        <v>74</v>
-      </c>
-      <c r="B67" s="1" t="s">
-        <v>83</v>
+        <v>68</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" t="s">
-        <v>75</v>
-      </c>
-      <c r="B68" s="1" t="s">
-        <v>48</v>
+        <v>69</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" t="s">
-        <v>77</v>
+        <v>71</v>
+      </c>
+      <c r="B70">
+        <v>2</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="B71">
-        <v>2499</v>
+        <v>1</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" t="s">
-        <v>79</v>
-      </c>
-      <c r="B72">
-        <v>4700</v>
+        <v>73</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>48</v>
+        <v>83</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>102</v>
+        <v>48</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2">
+      <c r="A76" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2">
+      <c r="A77" t="s">
+        <v>78</v>
+      </c>
+      <c r="B77">
+        <v>2499</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2">
+      <c r="A78" t="s">
+        <v>79</v>
+      </c>
+      <c r="B78">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2">
+      <c r="A79" t="s">
+        <v>80</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2">
+      <c r="A80" t="s">
+        <v>81</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2">
+      <c r="A81" t="s">
         <v>103</v>
       </c>
-      <c r="B75" t="s">
+      <c r="B81" t="s">
         <v>104</v>
       </c>
     </row>
